--- a/rsvp_forms/033_employee_christmas_party_form--rsvp_forms.xlsx
+++ b/rsvp_forms/033_employee_christmas_party_form--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'meat',_'label':_'meat'}</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Meat', 'label': 'Meat'}</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'vegetarian',_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Vegetarian', 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'vegan',_'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Vegan', 'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'attending',_'label':_'attending'}</t>
+          <t>attending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Attending', 'label': 'Attending'}</t>
+          <t>Attending</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'not_attending',_'label':_'not_attending'}</t>
+          <t>not_attending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Not Attending', 'label': 'Not Attending'}</t>
+          <t>Not Attending</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'undecided',_'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Undecided', 'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_3',_'label':_'more_than_3'}</t>
+          <t>more_than_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'More than 3', 'label': 'More than 3'}</t>
+          <t>More than 3</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
